--- a/docs/03_test/社員削除画面テスト.xlsx
+++ b/docs/03_test/社員削除画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E889812-42BB-4647-BD3A-4DA9C72D7657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5414D6-9CE9-40FB-978F-E2A3332FAADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3E5A4180-5218-4287-B943-DC5463A34754}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="社員削除テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -370,7 +370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -386,47 +386,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1092,34 +1089,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="12"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="4"/>
@@ -1133,76 +1130,76 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="11"/>
+      <c r="B34" s="14"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="13">
+      <c r="A37" s="5">
         <v>1</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="7"/>
+      <c r="B40" s="9"/>
       <c r="C40" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1212,6 +1209,8 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D35:I36"/>
+    <mergeCell ref="D37:I37"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
@@ -1221,8 +1220,6 @@
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:I36"/>
-    <mergeCell ref="D37:I37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
